--- a/apps/api/assets/vocabulary/初中/人教版/人教版初中英语七年级上册.xlsx
+++ b/apps/api/assets/vocabulary/初中/人教版/人教版初中英语七年级上册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D433"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -523,6 +523,16 @@
           <t>Good morning!</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">int. （上午见面时用语，非正式场合常说 Morning）早上好
@@ -603,6 +613,16 @@
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Good afternoon!</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -880,6 +900,16 @@
           <t>HB</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>abbr. 厚膛壁身管（Heavy Barrel）
@@ -915,6 +945,16 @@
           <t>BBC</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>abbr. 英国广播公司（British Broadcasting Corporation）</t>
@@ -947,6 +987,16 @@
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Bob</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -963,6 +1013,16 @@
           <t>Cindy</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>n. 辛迪（女子名，Cynthia的昵称）</t>
@@ -996,6 +1056,16 @@
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Eric</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1202,6 +1272,16 @@
           <t>in English</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 用英语；用英语说；用英语表达</t>
@@ -1572,6 +1652,16 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>abbr. [计量] 公斤（kilogram）</t>
@@ -2778,6 +2868,16 @@
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>first name</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -2820,6 +2920,16 @@
           <t>last name</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 姓
@@ -2950,6 +3060,16 @@
           <t>Gina</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
           <t>n. 吉娜 （Regina,Angelina等的昵称）</t>
@@ -3191,6 +3311,16 @@
           <t>Green</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
           <t>n. 绿色；青春
@@ -3624,6 +3754,16 @@
           <t>Have a good day!</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 祝你今天开心；祝一天愉快；度过愉快的一天</t>
@@ -4189,6 +4329,16 @@
           <t>pencil box</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 铅笔盒；文具盒；你的铅笔盒</t>
@@ -4461,6 +4611,16 @@
           <t>What about ...?</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 不；…怎样
@@ -4518,6 +4678,16 @@
       <c r="A181" s="2" t="inlineStr">
         <is>
           <t>thank you for ...</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -4583,6 +4753,16 @@
           <t>You're welcome.</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 不客气；别客气；不用谢</t>
@@ -4710,6 +4890,16 @@
       <c r="A190" s="2" t="inlineStr">
         <is>
           <t>ID card</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -4868,6 +5058,16 @@
           <t>ask ... for ...</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 要(价)；来找
@@ -5098,6 +5298,16 @@
           <t>a set of</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">det. 一套；一副
@@ -5394,6 +5604,16 @@
           <t>come on</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (演员)出台；进行(很好)；(暴风雨等)起；(病,苦痛等)加深
@@ -5697,6 +5917,16 @@
           <t>tape player</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 磁带录音机的放音装置；小型录音机；磁带放音机；磁带重放装置
@@ -5760,6 +5990,16 @@
       <c r="A236" s="2" t="inlineStr">
         <is>
           <t>model plane</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -6059,6 +6299,16 @@
           <t>soccer ball</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 足球；英式足球；足球体</t>
@@ -6186,6 +6436,16 @@
           <t>let's</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
           <t>让我们（let us的简写）</t>
@@ -6196,6 +6456,16 @@
       <c r="A256" s="2" t="inlineStr">
         <is>
           <t>let us</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -6561,6 +6831,16 @@
       <c r="A272" s="2" t="inlineStr">
         <is>
           <t>watch TV</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -6846,6 +7126,16 @@
           <t>Bill</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
           <t>n. [法] 法案；广告；账单；[金融] 票据；钞票；清单
@@ -7132,6 +7422,16 @@
           <t>think about</t>
         </is>
       </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 思考；探讨；为…费心思；想像
@@ -7189,6 +7489,16 @@
       <c r="A300" s="2" t="inlineStr">
         <is>
           <t>How about ...?</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -7781,6 +8091,16 @@
           <t>How much ...?</t>
         </is>
       </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">conj. 多少
@@ -8102,6 +8422,16 @@
           <t>Can I help you?</t>
         </is>
       </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 我能帮你吗；我能帮助你吗；我能帮你忙吗</t>
@@ -8209,6 +8539,16 @@
       <c r="A344" s="2" t="inlineStr">
         <is>
           <t>Here you are.</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -8652,6 +8992,16 @@
           <t>a pair of</t>
         </is>
       </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">det. 一双
@@ -9000,6 +9350,16 @@
           <t>Happy birthday!</t>
         </is>
       </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 生日快乐
@@ -9037,6 +9397,16 @@
           <t>How old ...?</t>
         </is>
       </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">conj. 多少岁
@@ -9071,6 +9441,16 @@
       <c r="A383" s="2" t="inlineStr">
         <is>
           <t>See you!</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
@@ -9521,6 +9901,16 @@
           <t>Have a good time!</t>
         </is>
       </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 过得愉快；很愉快
@@ -9628,6 +10018,16 @@
           <t>P.E.</t>
         </is>
       </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 体育（课）（全写为 physical education）
@@ -9862,6 +10262,16 @@
       <c r="A418" s="2" t="inlineStr">
         <is>
           <t>for sure</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
@@ -10017,6 +10427,16 @@
           <t>A.M.</t>
         </is>
       </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">abbr. 调幅；振幅调制；议员（威尔士议会成员）
@@ -10030,6 +10450,16 @@
           <t>P.M.</t>
         </is>
       </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
           <t>abbr. 下午（post meridiem）</t>
@@ -10085,6 +10515,16 @@
       <c r="A429" s="2" t="inlineStr">
         <is>
           <t>from ... to ...</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
